--- a/docs/hasil_pengujian_kriptografi.xlsx
+++ b/docs/hasil_pengujian_kriptografi.xlsx
@@ -1,46 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e1672cccecb5498a/Documents/Semester 5/secure-file-vault/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2BBBDA2527C4BA5A6972AF0B093FA9A259A3589C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BA01E62-EDF5-4646-AD74-BFF5BB94F32E}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hasil Pengujian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hasil Pengujian" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+  <si>
+    <t>Nama Berkas / Skenario</t>
+  </si>
+  <si>
+    <t>Ukuran (Bytes)</t>
+  </si>
+  <si>
+    <t>Waktu Enkripsi (ms)</t>
+  </si>
+  <si>
+    <t>Waktu Dekripsi (ms)</t>
+  </si>
+  <si>
+    <t>Entropi Cipherteks</t>
+  </si>
+  <si>
+    <t>Avalanche Effect (%)</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>1 KB Dummy</t>
+  </si>
+  <si>
+    <t>Entropi tinggi - ciphertext tampak acak</t>
+  </si>
+  <si>
+    <t>1 MB Dummy</t>
+  </si>
+  <si>
+    <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
+  </si>
+  <si>
+    <t>10 MB Dummy</t>
+  </si>
+  <si>
+    <t>Dokumen PDF</t>
+  </si>
+  <si>
+    <t>Entropi lebih rendah, kemungkinan karena ukuran data kecil</t>
+  </si>
+  <si>
+    <t>Gambar BMP Header</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,247 +113,358 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Waktu Enkripsi vs Dekripsi per Skenario</a:t>
             </a:r>
           </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Hasil Pengujian'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.9981481481481479E-2"/>
+          <c:y val="2.3518518518518518E-2"/>
+          <c:w val="0.94825925925925925"/>
+          <c:h val="0.89651851851851849"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Hasil Pengujian'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Waktu Enkripsi (ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Hasil Pengujian'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Hasil Pengujian'!$C$2:$C$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Hasil Pengujian'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Hasil Pengujian'!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1 KB Dummy</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1 MB Dummy</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 MB Dummy</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dokumen PDF</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Gambar BMP Header</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Hasil Pengujian'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>605.35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>482.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>679.44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>495.74</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>483.78</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AA05-4BD7-9961-78B15E264E88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Hasil Pengujian'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Waktu Dekripsi (ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Hasil Pengujian'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Hasil Pengujian'!$D$2:$D$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Hasil Pengujian'!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1 KB Dummy</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1 MB Dummy</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 MB Dummy</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dokumen PDF</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Gambar BMP Header</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Hasil Pengujian'!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>563.41999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>494.59</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>558.46</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>489.12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>501.74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AA05-4BD7-9961-78B15E264E88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Skenario</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Waktu (ms)</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.73139537037037039"/>
+          <c:y val="0.15623962962962964"/>
+          <c:w val="0.23332685185185184"/>
+          <c:h val="0.17011333333333334"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5400000" cy="2700000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,197 +751,158 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="63" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nama Berkas / Skenario</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ukuran (Bytes)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Waktu Enkripsi (ms)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Waktu Dekripsi (ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Entropi Cipherteks</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Avalanche Effect (%)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Keterangan</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1 KB Dummy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
         <v>1024</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>605.35</v>
       </c>
-      <c r="D2" t="n">
-        <v>563.42</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7.8326</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="D2">
+        <v>563.41999999999996</v>
+      </c>
+      <c r="E2">
+        <v>7.8326000000000002</v>
+      </c>
+      <c r="F2">
         <v>50.04</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
-        </is>
+      <c r="G2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1 MB Dummy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
         <v>1048576</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>482.6</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>494.59</v>
       </c>
-      <c r="E3" t="n">
-        <v>7.9998</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3">
+        <v>7.9997999999999996</v>
+      </c>
+      <c r="F3">
         <v>50.03</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
-        </is>
+      <c r="G3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10 MB Dummy</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
         <v>10485760</v>
       </c>
-      <c r="C4" t="n">
-        <v>679.4400000000001</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>679.44</v>
+      </c>
+      <c r="D4">
         <v>558.46</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>50</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
-        </is>
+      <c r="G4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dokumen PDF</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
         <v>66</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>495.74</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>489.12</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>5.8323</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>47.35</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Entropi lebih rendah, kemungkinan karena ukuran data kecil</t>
-        </is>
+      <c r="G5" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gambar BMP Header</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
         <v>554</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>483.78</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>501.74</v>
       </c>
-      <c r="E6" t="n">
-        <v>7.6163</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>7.6162999999999998</v>
+      </c>
+      <c r="F6">
         <v>49.71</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
-        </is>
+      <c r="G6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/hasil_pengujian_kriptografi.xlsx
+++ b/docs/hasil_pengujian_kriptografi.xlsx
@@ -164,30 +164,6 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Hasil Pengujian'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Hasil Pengujian'!$A$2:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Hasil Pengujian'!$C$2:$C$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
               <f>'Hasil Pengujian'!D1</f>
             </strRef>
           </tx>
@@ -198,12 +174,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Hasil Pengujian'!$A$2:$A$11</f>
+              <f>'Hasil Pengujian'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Hasil Pengujian'!$D$2:$D$11</f>
+              <f>'Hasil Pengujian'!$D$2:$D$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Hasil Pengujian'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Hasil Pengujian'!$A$2:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hasil Pengujian'!$E$2:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -277,7 +277,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -589,56 +589,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="63" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="63" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nama Berkas / Skenario</t>
+          <t>Nama Berkas</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ukuran (Bytes)</t>
+          <t>Algoritma</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Ukuran (byte)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Waktu Enkripsi (ms)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Waktu Dekripsi (ms)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entropi Plaintext</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Entropi Ciphertext</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avalanche Effect (%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dekripsi Identik</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
@@ -647,28 +659,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>File Teks (1 KB)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>File Teks 1 KB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1048</v>
       </c>
-      <c r="C2" t="n">
-        <v>515.9</v>
-      </c>
       <c r="D2" t="n">
-        <v>574.59</v>
+        <v>528.6</v>
       </c>
       <c r="E2" t="n">
+        <v>576.5</v>
+      </c>
+      <c r="F2" t="n">
         <v>4.9467</v>
       </c>
-      <c r="F2" t="n">
-        <v>7.8053</v>
-      </c>
       <c r="G2" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>7.8198</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Entropi tinggi - ciphertext tampak acak</t>
         </is>
@@ -677,58 +699,78 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>File Teks (100 KB)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4100</v>
+          <t>File Teks 1 KB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>494.2</v>
+        <v>1048</v>
       </c>
       <c r="D3" t="n">
-        <v>560.41</v>
+        <v>485</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0162</v>
+        <v>507.8</v>
       </c>
       <c r="F3" t="n">
-        <v>7.9527</v>
+        <v>4.9467</v>
       </c>
       <c r="G3" t="n">
-        <v>50.08</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
+        <v>7.7859</v>
+      </c>
+      <c r="H3" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Entropi tinggi - ciphertext tampak acak</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>File Teks (1 MB)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+          <t>File Teks 1 MB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1048576</v>
       </c>
-      <c r="C4" t="n">
-        <v>507.2</v>
-      </c>
       <c r="D4" t="n">
-        <v>544.85</v>
+        <v>477.81</v>
       </c>
       <c r="E4" t="n">
+        <v>500.03</v>
+      </c>
+      <c r="F4" t="n">
         <v>4.8803</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>7.9998</v>
       </c>
-      <c r="G4" t="n">
-        <v>50.01</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
@@ -737,28 +779,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>File Teks (10 MB)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10485760</v>
+          <t>File Teks 1 MB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>557.09</v>
+        <v>1048576</v>
       </c>
       <c r="D5" t="n">
-        <v>524.91</v>
+        <v>508.95</v>
       </c>
       <c r="E5" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="F5" t="n">
         <v>4.8803</v>
       </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
       <c r="G5" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>7.9998</v>
+      </c>
+      <c r="H5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
@@ -767,58 +819,78 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>File PDF</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1070</v>
+          <t>File Teks 10 MB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>508.73</v>
+        <v>10485760</v>
       </c>
       <c r="D6" t="n">
-        <v>479.85</v>
+        <v>584.59</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7621</v>
+        <v>525.04</v>
       </c>
       <c r="F6" t="n">
-        <v>7.8095</v>
+        <v>4.8803</v>
       </c>
       <c r="G6" t="n">
-        <v>50.07</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gambar Uncompressed BMP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>120054</v>
+          <t>File Teks 10 MB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>483.9</v>
+        <v>10485760</v>
       </c>
       <c r="D7" t="n">
-        <v>484.14</v>
+        <v>613.54</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7823</v>
+        <v>627.53</v>
       </c>
       <c r="F7" t="n">
-        <v>7.9984</v>
+        <v>4.8803</v>
       </c>
       <c r="G7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
@@ -827,28 +899,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gambar Compressed PNG</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>862</v>
+          <t>Dokumen PDF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>533.97</v>
+        <v>1070</v>
       </c>
       <c r="D8" t="n">
-        <v>480.87</v>
+        <v>495.43</v>
       </c>
       <c r="E8" t="n">
-        <v>6.6672</v>
+        <v>496.04</v>
       </c>
       <c r="F8" t="n">
-        <v>7.7789</v>
+        <v>5.7621</v>
       </c>
       <c r="G8" t="n">
-        <v>50.23</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>7.7999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Entropi tinggi - ciphertext tampak acak</t>
         </is>
@@ -857,90 +939,280 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>File Struktur Data JSON</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4100</v>
+          <t>Dokumen PDF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>485.15</v>
+        <v>1070</v>
       </c>
       <c r="D9" t="n">
-        <v>477.32</v>
+        <v>500.68</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0162</v>
+        <v>499.09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.9491</v>
+        <v>5.7621</v>
       </c>
       <c r="G9" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
+        <v>7.7959</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Entropi tinggi - ciphertext tampak acak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Simulasi Cipherteks Rusak (1-Byte Corrupt)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1070</v>
+          <t>Gambar BMP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>485.78</v>
+        <v>120054</v>
       </c>
       <c r="D10" t="n">
-        <v>490.06</v>
+        <v>506.09</v>
       </c>
       <c r="E10" t="n">
-        <v>5.7621</v>
+        <v>480.97</v>
       </c>
       <c r="F10" t="n">
-        <v>7.7827</v>
+        <v>0.7823</v>
       </c>
       <c r="G10" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
+        <v>7.9987</v>
+      </c>
+      <c r="H10" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Simulasi Bit-Flip Kunci (Avalanche Test)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1048576</v>
+          <t>Gambar BMP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>489.1</v>
+        <v>120054</v>
       </c>
       <c r="D11" t="n">
-        <v>604.14</v>
+        <v>494.36</v>
       </c>
       <c r="E11" t="n">
-        <v>4.8803</v>
+        <v>496.22</v>
       </c>
       <c r="F11" t="n">
-        <v>7.9998</v>
+        <v>0.7823</v>
       </c>
       <c r="G11" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>7.9988</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gambar JPG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2893</v>
+      </c>
+      <c r="D12" t="n">
+        <v>479.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>542.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.3027</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.931</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gambar JPG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2893</v>
+      </c>
+      <c r="D13" t="n">
+        <v>483.07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>476.08</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.3027</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.9351</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gambar PNG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AES-256-GCM</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>862</v>
+      </c>
+      <c r="D14" t="n">
+        <v>480.57</v>
+      </c>
+      <c r="E14" t="n">
+        <v>481.45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.6672</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.7579</v>
+      </c>
+      <c r="H14" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Entropi tinggi - ciphertext tampak acak</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gambar PNG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ChaCha20-Poly1305</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>862</v>
+      </c>
+      <c r="D15" t="n">
+        <v>492.56</v>
+      </c>
+      <c r="E15" t="n">
+        <v>497.42</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.6672</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.7917</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Entropi tinggi - ciphertext tampak acak</t>
         </is>
       </c>
     </row>

--- a/docs/hasil_pengujian_kriptografi.xlsx
+++ b/docs/hasil_pengujian_kriptografi.xlsx
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1048</v>
+        <v>1024</v>
       </c>
       <c r="D2" t="n">
-        <v>528.6</v>
+        <v>594.49</v>
       </c>
       <c r="E2" t="n">
-        <v>576.5</v>
+        <v>629.5599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9467</v>
+        <v>4.8781</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8198</v>
+        <v>7.8168</v>
       </c>
       <c r="H2" t="n">
-        <v>50.32</v>
+        <v>50.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1048</v>
+        <v>1024</v>
       </c>
       <c r="D3" t="n">
-        <v>485</v>
+        <v>493.51</v>
       </c>
       <c r="E3" t="n">
-        <v>507.8</v>
+        <v>495.9</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9467</v>
+        <v>4.8781</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7859</v>
+        <v>7.8054</v>
       </c>
       <c r="H3" t="n">
-        <v>49.92</v>
+        <v>49.82</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         <v>1048576</v>
       </c>
       <c r="D4" t="n">
-        <v>477.81</v>
+        <v>501.41</v>
       </c>
       <c r="E4" t="n">
-        <v>500.03</v>
+        <v>520.22</v>
       </c>
       <c r="F4" t="n">
         <v>4.8803</v>
@@ -763,7 +763,7 @@
         <v>7.9998</v>
       </c>
       <c r="H4" t="n">
-        <v>49.98</v>
+        <v>50.05</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -791,19 +791,19 @@
         <v>1048576</v>
       </c>
       <c r="D5" t="n">
-        <v>508.95</v>
+        <v>512.48</v>
       </c>
       <c r="E5" t="n">
-        <v>498.9</v>
+        <v>490.57</v>
       </c>
       <c r="F5" t="n">
         <v>4.8803</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9998</v>
+        <v>7.9999</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>49.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         <v>10485760</v>
       </c>
       <c r="D6" t="n">
-        <v>584.59</v>
+        <v>556.1</v>
       </c>
       <c r="E6" t="n">
-        <v>525.04</v>
+        <v>534.51</v>
       </c>
       <c r="F6" t="n">
         <v>4.8803</v>
@@ -871,10 +871,10 @@
         <v>10485760</v>
       </c>
       <c r="D7" t="n">
-        <v>613.54</v>
+        <v>612.25</v>
       </c>
       <c r="E7" t="n">
-        <v>627.53</v>
+        <v>582.8099999999999</v>
       </c>
       <c r="F7" t="n">
         <v>4.8803</v>
@@ -883,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>49.99</v>
+        <v>50</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -908,22 +908,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1070</v>
+        <v>12303288</v>
       </c>
       <c r="D8" t="n">
-        <v>495.43</v>
+        <v>566.83</v>
       </c>
       <c r="E8" t="n">
-        <v>496.04</v>
+        <v>579.38</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7621</v>
+        <v>7.9943</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7999</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>48.97</v>
+        <v>50</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
       </c>
     </row>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1070</v>
+        <v>12303288</v>
       </c>
       <c r="D9" t="n">
-        <v>500.68</v>
+        <v>682.95</v>
       </c>
       <c r="E9" t="n">
-        <v>499.09</v>
+        <v>662.64</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7621</v>
+        <v>7.9943</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7959</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>50.43</v>
+        <v>50.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
       </c>
     </row>
@@ -988,22 +988,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>120054</v>
+        <v>6635574</v>
       </c>
       <c r="D10" t="n">
-        <v>506.09</v>
+        <v>557.51</v>
       </c>
       <c r="E10" t="n">
-        <v>480.97</v>
+        <v>530.11</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7823</v>
+        <v>6.6398</v>
       </c>
       <c r="G10" t="n">
-        <v>7.9987</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>49.88</v>
+        <v>50</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1028,22 +1028,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120054</v>
+        <v>6635574</v>
       </c>
       <c r="D11" t="n">
-        <v>494.36</v>
+        <v>552.25</v>
       </c>
       <c r="E11" t="n">
-        <v>496.22</v>
+        <v>549.53</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7823</v>
+        <v>6.6398</v>
       </c>
       <c r="G11" t="n">
-        <v>7.9988</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>50.07</v>
+        <v>50</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2893</v>
+        <v>107357</v>
       </c>
       <c r="D12" t="n">
-        <v>479.8</v>
+        <v>505.4</v>
       </c>
       <c r="E12" t="n">
-        <v>542.8</v>
+        <v>583.23</v>
       </c>
       <c r="F12" t="n">
-        <v>7.3027</v>
+        <v>7.5312</v>
       </c>
       <c r="G12" t="n">
-        <v>7.931</v>
+        <v>7.9982</v>
       </c>
       <c r="H12" t="n">
-        <v>49.87</v>
+        <v>50.01</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2893</v>
+        <v>107357</v>
       </c>
       <c r="D13" t="n">
-        <v>483.07</v>
+        <v>505.55</v>
       </c>
       <c r="E13" t="n">
-        <v>476.08</v>
+        <v>502.55</v>
       </c>
       <c r="F13" t="n">
-        <v>7.3027</v>
+        <v>7.5312</v>
       </c>
       <c r="G13" t="n">
-        <v>7.9351</v>
+        <v>7.9983</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>49.99</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>862</v>
+        <v>1400325</v>
       </c>
       <c r="D14" t="n">
-        <v>480.57</v>
+        <v>513.77</v>
       </c>
       <c r="E14" t="n">
-        <v>481.45</v>
+        <v>518.92</v>
       </c>
       <c r="F14" t="n">
-        <v>6.6672</v>
+        <v>7.9882</v>
       </c>
       <c r="G14" t="n">
-        <v>7.7579</v>
+        <v>7.9999</v>
       </c>
       <c r="H14" t="n">
-        <v>49.22</v>
+        <v>49.99</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>862</v>
+        <v>1400325</v>
       </c>
       <c r="D15" t="n">
-        <v>492.56</v>
+        <v>512.41</v>
       </c>
       <c r="E15" t="n">
-        <v>497.42</v>
+        <v>500.19</v>
       </c>
       <c r="F15" t="n">
-        <v>6.6672</v>
+        <v>7.9882</v>
       </c>
       <c r="G15" t="n">
-        <v>7.7917</v>
+        <v>7.9999</v>
       </c>
       <c r="H15" t="n">
-        <v>50.84</v>
+        <v>49.99</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Entropi tinggi - ciphertext tampak acak</t>
+          <t>Entropi mendekati maksimum (8.0) - ciphertext acak sempurna</t>
         </is>
       </c>
     </row>
